--- a/backend_fastapi/backend_fastapi/media/excel/15_Other.xlsx
+++ b/backend_fastapi/backend_fastapi/media/excel/15_Other.xlsx
@@ -428,15 +428,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN6"/>
+  <dimension ref="A1:AN8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
     <col width="32" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="29" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
     <col width="30" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
@@ -449,13 +449,13 @@
     <col width="22" customWidth="1" min="16" max="16"/>
     <col width="20" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="11" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
     <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="11" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="27" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
-    <col width="19" customWidth="1" min="25" max="25"/>
+    <col width="16" customWidth="1" min="25" max="25"/>
     <col width="19" customWidth="1" min="26" max="26"/>
     <col width="29" customWidth="1" min="27" max="27"/>
     <col width="20" customWidth="1" min="28" max="28"/>
@@ -678,70 +678,70 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Smith, Schaefer and Gonzalez</t>
+          <t>Porter-Perkins</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Unit 1154 Box 8683
-DPO AE 34629</t>
+          <t>88652 James Loaf
+East Alyssamouth, KS 81684</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Smith, Schaefer and Gonzalez</t>
+          <t>Porter-Perkins</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>902-72-8574</t>
+          <t>929-76-1260</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Smith-Petersen</t>
+          <t>Castaneda LLC</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>05025 Mary Fall
-Mackside, OR 70036</t>
+          <t>19558 Fry Causeway
+East Chelseytown, MD 95490</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Smith-Petersen</t>
+          <t>Castaneda LLC</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>934-70-6847</t>
+          <t>940-86-9734</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>22083742</v>
+        <v>46506594</v>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2014-03-01</t>
+          <t>2012-03-12</t>
         </is>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="n">
-        <v>7200</v>
+        <v>1335.86</v>
       </c>
       <c r="S2" t="n">
-        <v>720</v>
+        <v>133.59</v>
       </c>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="n">
-        <v>7920</v>
+        <v>1469.45</v>
       </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr"/>
@@ -752,7 +752,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>10% → 720.0</t>
+          <t>10% → 133.59</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr"/>
@@ -763,14 +763,21 @@
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>IBAN:GB62IACN00896958403438</t>
+          <t>IBAN:GB49GJRS28729607733931</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>YILONG 4'x6' All over
-Handmade Carpet Dining Room
-Hand Knotted Silk Rugs 082B x2.0 @ 3600.0 = 7920.0</t>
+          <t>Nintendo 3DS Handheld Console
+Purple x5.0 @ 98.99 = 544.45 | PocketGo Bittboy v2 White
+Retro Video Game Portable
+Console - 3.5 IPS display x4.0 @ 39.0 = 171.6 | Sony PlayStation 3 Slim 120GB
+Black Console x4.0 @ 99.99 = 439.96 | Microsoft Xbox 360 - White -
+Console, Power Supply, AV
+Cables *Tested, Working* x1.0 @ 39.95 = 43.95 | SONY Playstation2 Console
+SCPH-39000 " Aqua Color " /
+TESTED 11181 x1.0 @ 45.0 = 49.5 | Nintendo 64 Console "Perfect" +
+Lot Games "6 Games" x1.0 @ 200.0 = 220.0</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
@@ -784,7 +791,7 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>0.948</v>
+        <v>0.871</v>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
@@ -797,73 +804,69 @@
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>Items sum (7920.0) ≈ Subtotal (7200.0). Diff: 720.00 (10.0%); Recommended field missing: Due date (due_date)</t>
+          <t>Items sum (1469.46) ≈ Subtotal (1335.86). Diff: 133.60 (10.0%); Recommended field missing: Due date (due_date)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Jones, Davis and Moses</t>
+          <t>Lozano, Wang and Smith</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>6622 Davis Court
-Curtismouth, MA 23635</t>
+          <t>8162 Dunn Radial
+Lauraland, ID 83827</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Jones, Davis and Moses</t>
+          <t>Lozano, Wang and Smith</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Cox LLC</t>
+          <t>Evans, Curtis and Salinas</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>164 Dean Bypass
-Lake Stephenchester, AR 78025</t>
+          <t>13078 Mora Garden
+Morseberg, WV 48959</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Cox LLC</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>967-86-2378</t>
-        </is>
-      </c>
+          <t>Evans, Curtis and Salinas</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="n">
-        <v>89299747</v>
+        <v>56908352</v>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2018-04-14</t>
+          <t>2015-01-11</t>
         </is>
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="n">
-        <v>353.64</v>
+        <v>171.01</v>
       </c>
       <c r="S3" t="n">
-        <v>35.36</v>
+        <v>17.1</v>
       </c>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="n">
-        <v>389</v>
+        <v>188.11</v>
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
@@ -874,7 +877,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>10% → 35.36</t>
+          <t>10% → 17.1</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr"/>
@@ -885,21 +888,17 @@
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>IBAN:GB41VOYB69288847998165</t>
+          <t>IBAN:GB68RRBM34982962207975</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>Vintage Crystal Red Wine
-Glasses NOS West Germany
-1983 6 10 ounce elegant stems x5.0 @ 35.45 = 194.98 | Wine Bottle Holder From Costa
-Rica Has A Parrot Painted On It x5.0 @ 5.0 = 27.5 | Birthday Girl Wine Glass by
-Lolita x2.0 @ 23.75 = 52.25 | Metal Storage Shelf Wine Glass
-Rack Wine Glasses for The
-Cabinet x2.0 @ 22.42 = 49.32 | Unicorn Wine Bottle Display x3.0 @ 15.85 = 52.3 | 100pcs Heat Shrink Capsules
-PVC Wine Bottle Caps
-Shrinkable Seal Film Covers
-3cm x2.0 @ 5.75 = 12.65</t>
+          <t>Rage By Bob Woodward -
+Donald Trump NEW
+HARDCOVER Sept 2020 x5.0 @ 22.93 = 126.12 | Spectacular Ireland Coffee
+Table Book - very large x4.0 @ 10.0 = 44.0 | The Complete Life's Little
+Instruction Book by Brown, H.
+Jackson, Jr. x4.0 @ 4.09 = 18.0</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
@@ -913,7 +912,7 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>0.946</v>
+        <v>0.93</v>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
@@ -926,62 +925,88 @@
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>Items sum (389.0) ≈ Subtotal (353.64). Diff: 35.36 (10.0%); Recommended field missing: Due date (due_date)</t>
+          <t>Items sum (188.12) ≈ Subtotal (171.01). Diff: 17.11 (10.0%); Recommended field missing: Due date (due_date)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MARJANE OUARZAZATE</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
+          <t>Kerr, Ryan and Gomez</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>8069 Nicholas Greens
+Lake Vincentbury, RI 06574</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Kerr, Ryan and Gomez</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>TP:47107678</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>5201XXXXX6713</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>929-82-4759</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Mason Ltd</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>8053 Friedman Burg
+Patrickfort, FL 71567</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Mason Ltd</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>991-91-7229</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>15001300</v>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2014-02-18</t>
         </is>
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
+      <c r="R4" t="n">
+        <v>297.35</v>
+      </c>
       <c r="S4" t="n">
-        <v>5.917</v>
+        <v>29.73</v>
       </c>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="n">
-        <v>35.5</v>
+        <v>327.08</v>
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr">
         <is>
-          <t>MAD</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>20.00% → 5.9167</t>
+          <t>10% → None</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr"/>
@@ -990,11 +1015,24 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>IBAN:GB32MKCO74382010852522</t>
+        </is>
+      </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>(5)8410663018663
-SANDWICH CREME CHOCO = 35.5 | SURGELE @ 35.5 | ESPECES = 36.0</t>
+          <t>100Pcs Wall Stickers Home
+Decor Glow In The Dark Star
+sticker Decal Kids room x1.0 @ 1.7 = 1.87 | PUMA Boys Kids Athletic Shoes
+Flats Plimsouls Gray Black
+Denim size 12C x3.0 @ 19.0 = 62.7 | Joma Youth Boys Gol 205 Piso
+Multitaco Soccer Cleats 2.5
+White Blue Yellow NEW x5.0 @ 19.99 = 109.94 | Fila Boys Skele-Toes Bay RNR 3
+Black Running Shoes 11
+Medium (D) Little Kid 9953 x3.0 @ 10.25 = 33.83 | Kid Connection Kids Winter
+Waterproof Boots Size 5 Cozy &amp;
+Warm Slipn On Booties x5.0 @ 21.59 = 118.75</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
@@ -1008,7 +1046,7 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0.576</v>
+        <v>0.539</v>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
@@ -1021,73 +1059,73 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>Recommended field missing: Customer name (customer_name); Recommended field missing: Due date (due_date); Recommended field missing: Invoice ID (invoice_id)</t>
+          <t>Items sum (327.09) ≈ Subtotal (297.35). Diff: 29.74 (10.0%); Recommended field missing: Due date (due_date)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Schwartz, Flynn and Jackson</t>
+          <t>Smith, Schaefer and Gonzalez</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>59888 Dawn Valley Suite 242
-New Marilyn, WA 49740</t>
+          <t>Unit 1154 Box 8683
+DPO AE 34629</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Schwartz, Flynn and Jackson</t>
+          <t>Smith, Schaefer and Gonzalez</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Wilson PLC</t>
+          <t>Smith-Petersen</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>674 Leon Cape Suite 819
-Burtonstad, NE 12662</t>
+          <t>05025 Mary Fall
+Mackside, OR 70036</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Wilson PLC</t>
+          <t>Smith-Petersen</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>963-73-0110</t>
+          <t>934-70-6847</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>94689364</v>
+        <v>22083742</v>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2015-01-12</t>
+          <t>2014-03-01</t>
         </is>
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="n">
-        <v>33776.06</v>
+        <v>7200</v>
       </c>
       <c r="S5" t="n">
-        <v>3377.61</v>
+        <v>720</v>
       </c>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="n">
-        <v>37153.67</v>
+        <v>7920</v>
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
@@ -1098,7 +1136,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>10% → 3377.61</t>
+          <t>10% → 720.0</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr"/>
@@ -1109,24 +1147,14 @@
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>IBAN:GB67GYBL21403855924419</t>
+          <t>IBAN:GB62IACN00896958403438</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>Yilong 5'x8' Handknotted Silk
-Area Rug Home Decor Kid
-Friendly Carpet L39B x4.0 @ 8000.0 = 35200.0 | Faux Fur Animal Print Hide Skin
-Rug Cowhide Area Rug Floor
-Mat Carpet 33.5"X43" x4.0 @ 26.03 = 114.53 | Garden Flower Carpet Quilted
-Bedroom Floor Princess Tapis
-Lace Rug Carpets x5.0 @ 45.5 = 250.25 | Double Dorje Carpet Tibetan
-Rug Handwoven by Artisans in
-Nepal x3.0 @ 297.0 = 980.1 | Egg Bathroom Rug Carpet Area
-Rugs Rug Floor Mats Nordic Chic
-Room Decor x2.0 @ 68.1 = 149.82 | Striped Contemporary Gabbeh
-Kashkoli Oriental Area Rug
-Handmade Wool Carpet 6x8 x1.0 @ 417.24 = 458.96</t>
+          <t>YILONG 4'x6' All over
+Handmade Carpet Dining Room
+Hand Knotted Silk Rugs 082B x2.0 @ 3600.0 = 7920.0</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
@@ -1140,7 +1168,7 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.946</v>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
@@ -1153,79 +1181,77 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>Items sum (37153.66) ≈ Subtotal (33776.06). Diff: 3377.60 (10.0%); Recommended field missing: Due date (due_date)</t>
+          <t>Items sum (7920.0) ≈ Subtotal (7200.0). Diff: 720.00 (10.0%); Recommended field missing: Due date (due_date)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Smith, Schaefer and Gonzalez</t>
+          <t>Proctor, Levy and Willis</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Unit 1154 Box 8683
-DPO AE 34629</t>
+          <t>2297 Jessica Locks Apt. 407
+Jonside, LA 78714</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Smith, Schaefer and Gonzalez</t>
+          <t>Proctor, Levy and Willis</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>902-72-8574</t>
+          <t>902-74-7536</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Smith-Petersen</t>
+          <t>Roth, Morris and Schultz</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>05025 Mary Fall
-Mackside, OR 70036</t>
+          <t>623 Rebekah Causeway
+Gregoryport, ND 69850</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Smith-Petersen</t>
+          <t>Roth, Morris and Schultz</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>934-70-6847</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>22083742</t>
-        </is>
+          <t>913-71-7249</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>44848471</v>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2014-03-01</t>
+          <t>2021-03-26</t>
         </is>
       </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="n">
-        <v>7200</v>
+        <v>762.4400000000001</v>
       </c>
       <c r="S6" t="n">
-        <v>720</v>
+        <v>76.23999999999999</v>
       </c>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="n">
-        <v>7920</v>
+        <v>838.6799999999999</v>
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
@@ -1236,7 +1262,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>10% → 720.0</t>
+          <t>10% → 76.24</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr"/>
@@ -1247,14 +1273,19 @@
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>IBAN:GB62IACN00896958403438</t>
+          <t>IBAN:GB89NZLM61247862676381</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>YILONG 4'x6' All over
-Handmade Carpet Dining Room
-Hand Knotted Silk Rugs 082B x2.0 @ 3600.0 = 7920.0</t>
+          <t>Adidas Baseball Youth Cleats
+Spikes Kids Shoes Black White
+Size 12K x2.0 @ 11.99 = 26.38 | PUMA RS DREAMER SUPER
+MARIO 64 NINTENDO Little Kids
+US 2.5 x5.0 @ 125.0 = 687.5 | Boys Black Dress Shoes x3.0 @ 4.5 = 14.85 | NWT VANS BOYS/YOUTH SK8-HI
+MTE SNEAKERS/SHOES SIZE
+13.BRAND NEW FOR 2020!
+WOW! x4.0 @ 24.99 = 109.96</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
@@ -1268,7 +1299,7 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>0.948</v>
+        <v>0.851</v>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
@@ -1281,7 +1312,256 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>Items sum (7920.0) ≈ Subtotal (7200.0). Diff: 720.00 (10.0%); Recommended field missing: Due date (due_date)</t>
+          <t>Items sum (838.69) ≈ Subtotal (762.44). Diff: 76.25 (10.0%); Recommended field missing: Due date (due_date)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Burns, King and Serrano</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>75240 Munoz Bypass Suite 960
+East Tylerton, WA 04004</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Burns, King and Serrano</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>913-91-8891</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Bryant-Wall</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>21372 Nelson Fork Suite 152
+North Pamela, OK 82764</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Bryant-Wall</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>995-75-2976</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>34967709</v>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2018-01-16</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="n">
+        <v>499.98</v>
+      </c>
+      <c r="S7" t="n">
+        <v>50</v>
+      </c>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="n">
+        <v>549.98</v>
+      </c>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>10% → 50.0</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>IBAN:GB47XEBQ87721203651804</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>Nintendo 64 console complete
+in box with extra controller x2.0 @ 249.99 = 549.98</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.947</v>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>INVOICE</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>Items sum (549.98) ≈ Subtotal (499.98). Diff: 50.00 (10.0%); Recommended field missing: Due date (due_date)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Davis, Evans and Cooper</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>475 Daniel Port
+Moralesborough, OK 44662</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Davis, Evans and Cooper</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Stephens-Goodman</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>5197 Rebekah Stravenue Suite 498
+New Nicholasland, VA 18645</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Stephens-Goodman</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>24342647</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2020-05-07</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="n">
+        <v>4112.98</v>
+      </c>
+      <c r="S8" t="n">
+        <v>411.3</v>
+      </c>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="n">
+        <v>4524.28</v>
+      </c>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>10% → 411.3</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>IBAN:GB05CPFN10349037207241</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>15"x15" White Marble Coffee
+Table Top With 15" Tall Stand
+Semi Precious Art Deco x4.0 @ 575.99 = 2534.36 | 12" Marble Lapis Inlay Chess
+Table Top With 2" Pieces &amp; 15"
+Wooden Stand W537 x3.0 @ 444.6 = 1467.18 | 18"x18" White Hand Curved Top
+Coffee Table Inlay Decorative
+Gift For Her Wedding x1.0 @ 475.22 = 522.74</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.9419999999999999</v>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>INVOICE</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>Items sum (4524.28) ≈ Subtotal (4112.98). Diff: 411.30 (10.0%); Recommended field missing: Due date (due_date)</t>
         </is>
       </c>
     </row>
@@ -1296,7 +1576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -1348,23 +1628,23 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Schwartz, Flynn and Jackson</t>
+          <t>Smith, Schaefer and Gonzalez</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>37153.67</v>
+        <v>7920</v>
       </c>
       <c r="D2" t="n">
-        <v>37153.67</v>
+        <v>7920</v>
       </c>
       <c r="E2" t="n">
-        <v>37153.67</v>
+        <v>7920</v>
       </c>
       <c r="F2" t="n">
-        <v>37153.67</v>
+        <v>7920</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -1375,23 +1655,23 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Smith, Schaefer and Gonzalez</t>
+          <t>Davis, Evans and Cooper</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>15840</v>
+        <v>4524.28</v>
       </c>
       <c r="D3" t="n">
-        <v>7920</v>
+        <v>4524.28</v>
       </c>
       <c r="E3" t="n">
-        <v>7920</v>
+        <v>4524.28</v>
       </c>
       <c r="F3" t="n">
-        <v>7920</v>
+        <v>4524.28</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -1402,23 +1682,23 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Jones, Davis and Moses</t>
+          <t>Porter-Perkins</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>778</v>
+        <v>1469.45</v>
       </c>
       <c r="D4" t="n">
-        <v>389</v>
+        <v>1469.45</v>
       </c>
       <c r="E4" t="n">
-        <v>389</v>
+        <v>1469.45</v>
       </c>
       <c r="F4" t="n">
-        <v>389</v>
+        <v>1469.45</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -1429,27 +1709,108 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MARJANE OUARZAZATE</t>
+          <t>Proctor, Levy and Willis</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>35.5</v>
+        <v>838.6799999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>35.5</v>
+        <v>838.6799999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>35.5</v>
+        <v>838.6799999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>35.5</v>
+        <v>838.6799999999999</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>MAD</t>
+          <t>USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Burns, King and Serrano</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>549.98</v>
+      </c>
+      <c r="D6" t="n">
+        <v>549.98</v>
+      </c>
+      <c r="E6" t="n">
+        <v>549.98</v>
+      </c>
+      <c r="F6" t="n">
+        <v>549.98</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Kerr, Ryan and Gomez</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="n">
+        <v>327.08</v>
+      </c>
+      <c r="D7" t="n">
+        <v>327.08</v>
+      </c>
+      <c r="E7" t="n">
+        <v>327.08</v>
+      </c>
+      <c r="F7" t="n">
+        <v>327.08</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Lozano, Wang and Smith</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="n">
+        <v>188.11</v>
+      </c>
+      <c r="D8" t="n">
+        <v>188.11</v>
+      </c>
+      <c r="E8" t="n">
+        <v>188.11</v>
+      </c>
+      <c r="F8" t="n">
+        <v>188.11</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>USD</t>
         </is>
       </c>
     </row>
